--- a/data-manipulation-scripts/sheets-cleanup/sheets/RETENTOR PINHAO.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/RETENTOR PINHAO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -101,6 +101,12 @@
   </si>
   <si>
     <t>RETENTOR PINHAO TRILHA CB2050 TWISTER 2016</t>
+  </si>
+  <si>
+    <t>7895099124439</t>
+  </si>
+  <si>
+    <t>RETENTOR PINHA IRON CG FAN TITAN 2000 KS/ TITAN150 041646</t>
   </si>
 </sst>
 </file>
@@ -864,10 +870,38 @@
       <c r="Z14" s="6"/>
     </row>
     <row r="15">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
+      <c r="A15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="7">
+        <v>16.0</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="6"/>
+      <c r="T15" s="6"/>
+      <c r="U15" s="6"/>
+      <c r="V15" s="6"/>
+      <c r="W15" s="6"/>
+      <c r="X15" s="6"/>
+      <c r="Y15" s="6"/>
+      <c r="Z15" s="6"/>
     </row>
     <row r="16">
       <c r="A16" s="8"/>

--- a/data-manipulation-scripts/sheets-cleanup/sheets/RETENTOR PINHAO.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/RETENTOR PINHAO.xlsx
@@ -167,7 +167,7 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -437,7 +437,9 @@
       <c r="C2" s="4">
         <v>5.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="5">
+        <v>12.0</v>
+      </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -471,7 +473,9 @@
       <c r="C3" s="4">
         <v>19.0</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="5">
+        <v>12.0</v>
+      </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -505,7 +509,9 @@
       <c r="C4" s="4">
         <v>5.0</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="5">
+        <v>12.0</v>
+      </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -539,7 +545,9 @@
       <c r="C5" s="7">
         <v>4.0</v>
       </c>
-      <c r="D5" s="6"/>
+      <c r="D5" s="5">
+        <v>12.0</v>
+      </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -573,7 +581,9 @@
       <c r="C6" s="7">
         <v>5.0</v>
       </c>
-      <c r="D6" s="6"/>
+      <c r="D6" s="5">
+        <v>12.0</v>
+      </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -607,7 +617,9 @@
       <c r="C7" s="7">
         <v>10.0</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="5">
+        <v>12.0</v>
+      </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -641,7 +653,9 @@
       <c r="C8" s="7">
         <v>7.0</v>
       </c>
-      <c r="D8" s="6"/>
+      <c r="D8" s="5">
+        <v>12.0</v>
+      </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
@@ -675,7 +689,9 @@
       <c r="C9" s="7">
         <v>3.0</v>
       </c>
-      <c r="D9" s="6"/>
+      <c r="D9" s="5">
+        <v>12.0</v>
+      </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
@@ -709,7 +725,9 @@
       <c r="C10" s="7">
         <v>4.0</v>
       </c>
-      <c r="D10" s="6"/>
+      <c r="D10" s="5">
+        <v>12.0</v>
+      </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
@@ -743,7 +761,9 @@
       <c r="C11" s="7">
         <v>11.0</v>
       </c>
-      <c r="D11" s="6"/>
+      <c r="D11" s="5">
+        <v>12.0</v>
+      </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
@@ -777,7 +797,9 @@
       <c r="C12" s="7">
         <v>5.0</v>
       </c>
-      <c r="D12" s="6"/>
+      <c r="D12" s="5">
+        <v>12.0</v>
+      </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
@@ -811,7 +833,9 @@
       <c r="C13" s="7">
         <v>2.0</v>
       </c>
-      <c r="D13" s="6"/>
+      <c r="D13" s="5">
+        <v>12.0</v>
+      </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
@@ -845,7 +869,9 @@
       <c r="C14" s="7">
         <v>9.0</v>
       </c>
-      <c r="D14" s="6"/>
+      <c r="D14" s="5">
+        <v>12.0</v>
+      </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
@@ -879,7 +905,9 @@
       <c r="C15" s="7">
         <v>16.0</v>
       </c>
-      <c r="D15" s="6"/>
+      <c r="D15" s="5">
+        <v>12.0</v>
+      </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
